--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,21 +457,21 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -480,67 +480,67 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -549,34 +549,34 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T1_AbreCierra</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -590,39 +590,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -641,11 +641,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -655,20 +655,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>T2_AbreCierra</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -678,43 +678,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -724,30 +724,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -756,11 +756,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -770,20 +770,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T3_AbreCierra</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -793,43 +793,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -839,20 +839,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -862,20 +862,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -885,20 +885,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>T4_Cierra</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -908,16 +908,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -954,16 +954,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -977,7 +977,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -986,7 +986,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1000,16 +1000,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1023,16 +1023,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1041,21 +1041,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1087,21 +1087,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1115,16 +1115,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1138,11 +1138,80 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9</v>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>35</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>35</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PARCIAL</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -494,11 +494,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -512,7 +512,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -535,16 +535,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -558,12 +558,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -609,11 +609,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -627,16 +627,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -678,11 +678,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -696,16 +696,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
@@ -719,16 +719,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="14">
@@ -742,7 +742,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -765,16 +765,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -793,11 +793,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -816,11 +816,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="18">
@@ -839,7 +839,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -885,11 +885,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -926,16 +926,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="23">
@@ -949,16 +949,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -972,12 +972,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -995,16 +995,16 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1018,16 +1018,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -1046,11 +1046,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
@@ -1087,16 +1087,16 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="31">
@@ -1138,11 +1138,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="32">

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -494,11 +494,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -512,16 +512,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="5">
@@ -540,11 +540,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -563,11 +563,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -586,11 +586,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
@@ -627,16 +627,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="10">
@@ -655,7 +655,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -678,11 +678,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -696,16 +696,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -719,16 +719,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -742,7 +742,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -765,16 +765,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -793,7 +793,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -834,16 +834,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -857,7 +857,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -880,16 +880,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="21">
@@ -903,16 +903,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22">
@@ -926,16 +926,16 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
@@ -949,16 +949,16 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="24">
@@ -972,16 +972,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="25">
@@ -995,12 +995,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1018,16 +1018,16 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -1046,11 +1046,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -1064,16 +1064,16 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="29">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1115,11 +1115,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E31" t="n">

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>worker_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>nombre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>dia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>entrada</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>duracion</t>
         </is>
@@ -457,11 +445,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>T1_AbreCierra</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -471,20 +459,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>T1_AbreCierra</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -494,20 +482,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>T1_AbreCierra</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -517,20 +505,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>T1_AbreCierra</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -549,11 +537,11 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T1_AbreCierra</t>
+          <t>T1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -563,20 +551,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>T2_AbreCierra</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -586,20 +574,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T2_AbreCierra</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -609,43 +597,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T2_AbreCierra</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T2_AbreCierra</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -664,11 +652,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>T2_AbreCierra</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -678,25 +666,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>T3_AbreCierra</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -710,16 +698,16 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>T3_AbreCierra</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -728,26 +716,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>T3_AbreCierra</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -756,11 +744,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>T3_AbreCierra</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -770,7 +758,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -779,11 +767,11 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>T3_AbreCierra</t>
+          <t>T3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -793,122 +781,122 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>T4_Cierra</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>T4_Cierra</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>T4_Cierra</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>T4_Cierra</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>T4_Cierra</t>
+          <t>T4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -917,7 +905,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -926,21 +914,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -954,16 +942,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -977,16 +965,16 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1000,16 +988,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1023,16 +1011,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1046,16 +1034,16 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1069,16 +1057,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1087,21 +1075,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1110,21 +1098,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1133,84 +1121,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>35</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>35</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>35</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>PARCIAL</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
         <v>8</v>
       </c>
     </row>

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -454,16 +454,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -500,16 +500,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -574,11 +574,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -592,16 +592,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -620,11 +620,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -666,11 +666,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -684,12 +684,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
@@ -730,12 +730,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -758,11 +758,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -781,11 +781,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -799,12 +799,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -822,16 +822,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -845,16 +845,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -873,11 +873,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -896,11 +896,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
@@ -919,11 +919,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -937,12 +937,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -960,16 +960,16 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -988,11 +988,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1011,11 +1011,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
@@ -1080,11 +1080,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -1126,11 +1126,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -454,12 +454,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -468,7 +468,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -482,16 +482,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -505,16 +505,16 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -528,16 +528,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -551,16 +551,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -574,16 +574,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -592,21 +592,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -629,7 +629,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -643,16 +643,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -666,16 +666,16 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -684,21 +684,21 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -707,12 +707,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -721,7 +721,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -730,21 +730,21 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -758,16 +758,16 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -781,16 +781,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -822,12 +822,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -836,7 +836,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -845,12 +845,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -859,7 +859,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -873,16 +873,16 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -914,21 +914,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -951,7 +951,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -960,12 +960,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -974,7 +974,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1015,12 +1015,12 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1098,21 +1098,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1121,16 +1121,131 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>35</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>35</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>35</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>6</v>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/calendario_generado.xlsx
+++ b/data/outputs/calendario_generado.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -528,11 +528,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -574,11 +574,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -643,11 +643,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -689,11 +689,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -804,11 +804,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -873,11 +873,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -919,11 +919,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
@@ -1149,11 +1149,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -1172,11 +1172,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -1195,11 +1195,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E35" t="n">
